--- a/data/edu_comp_es.xlsx
+++ b/data/edu_comp_es.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Grants\Datos CV\archivos (1)\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Mile_CV\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4BC6D9-1A42-4CE4-82AD-68A66B7A0729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E66796-49E1-41F8-9509-5469877885AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>what</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t xml:space="preserve">Bogotá, Colombia </t>
+  </si>
+  <si>
+    <t>Especialización en Docencia en Educación Superior</t>
   </si>
 </sst>
 </file>
@@ -110,9 +113,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -150,7 +153,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -256,7 +259,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -398,7 +401,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -406,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.33203125" customWidth="1"/>
@@ -435,10 +438,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -449,15 +452,29 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>2020</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>2019</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
     </row>
